--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0569EEF3-1072-9248-9E3D-70B15FA830CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C00FBA-8A26-0046-AD07-431DEDBA2790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12480" yWindow="660" windowWidth="22080" windowHeight="20060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="940" yWindow="660" windowWidth="33620" windowHeight="17440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runners" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="306">
   <si>
     <t>#</t>
   </si>
@@ -100,9 +100,6 @@
     <t>Gretchen Chiques</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>GC</t>
   </si>
   <si>
@@ -229,9 +226,6 @@
     <t>Lisset Velasquez</t>
   </si>
   <si>
-    <t>LV</t>
-  </si>
-  <si>
     <t>lisset_velazquez@yahoo.com</t>
   </si>
   <si>
@@ -256,15 +250,6 @@
     <t>EU</t>
   </si>
   <si>
-    <t>John McDaniel</t>
-  </si>
-  <si>
-    <t>JM</t>
-  </si>
-  <si>
-    <t>863-214-1704</t>
-  </si>
-  <si>
     <t>Role</t>
   </si>
   <si>
@@ -289,12 +274,6 @@
     <t>Still Full of Egrets</t>
   </si>
   <si>
-    <t>I Egret this Already</t>
-  </si>
-  <si>
-    <t>DRAFT</t>
-  </si>
-  <si>
     <t>Runner</t>
   </si>
   <si>
@@ -415,78 +394,30 @@
     <t>Johnny</t>
   </si>
   <si>
-    <t>Tent Sleeping John M (sleeps 1)</t>
-  </si>
-  <si>
-    <t>John M</t>
-  </si>
-  <si>
     <t>Tent Sleeping Ozark1 (sleeps 20)</t>
   </si>
   <si>
-    <t>PENDING</t>
-  </si>
-  <si>
-    <t>Person1+Person2+Person3+Person4+Person5+Person6+Person7+Person8</t>
-  </si>
-  <si>
     <t>Tent Sleeping Ozark2 (sleeps 4)</t>
   </si>
   <si>
-    <t>Person1+Person2</t>
-  </si>
-  <si>
     <t>Tent Sleeping Claudia (sleeps 2)</t>
   </si>
   <si>
-    <t>Claudia+Person2</t>
-  </si>
-  <si>
     <t>Tent Sleeping Embark (sleeps 1)</t>
   </si>
   <si>
-    <t>Person1</t>
-  </si>
-  <si>
     <t>Tent Sleeping Coleman (sleeps 2)</t>
   </si>
   <si>
     <t>Car 1 (Chiara fits 5)</t>
   </si>
   <si>
-    <t>Chiara+Person2+Person3+Person4+Person5</t>
-  </si>
-  <si>
     <t>Car 2 (Dan fits 5)</t>
   </si>
   <si>
-    <t>Dan+Person2+Person3+Person4+Person5</t>
-  </si>
-  <si>
-    <t>Car 3 Johnny</t>
-  </si>
-  <si>
-    <t>Car 4 Lynette</t>
-  </si>
-  <si>
-    <t>Car 5 Gretchen</t>
-  </si>
-  <si>
     <t>Gretchen from Cape Coral</t>
   </si>
   <si>
-    <t>Car 6 John M</t>
-  </si>
-  <si>
-    <t>John coming from Sebring</t>
-  </si>
-  <si>
-    <t>Car 7 INPUT</t>
-  </si>
-  <si>
-    <t>Car 8 INPUT</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -679,9 +610,6 @@
     <t>Headlamp (required)</t>
   </si>
   <si>
-    <t>Headlamp Backup</t>
-  </si>
-  <si>
     <t>Hand Flashlight</t>
   </si>
   <si>
@@ -760,9 +688,6 @@
     <t>Toilet Tent</t>
   </si>
   <si>
-    <t>borrowed from Elian</t>
-  </si>
-  <si>
     <t>Toilet Bags</t>
   </si>
   <si>
@@ -916,18 +841,6 @@
     <t>786-525-6121</t>
   </si>
   <si>
-    <t>Elizabeth Velazquez</t>
-  </si>
-  <si>
-    <t>305-721-9423</t>
-  </si>
-  <si>
-    <t>Brandee Helms</t>
-  </si>
-  <si>
-    <t>863-257-5153</t>
-  </si>
-  <si>
     <t>Parent</t>
   </si>
   <si>
@@ -953,16 +866,111 @@
   </si>
   <si>
     <t>David Umulis</t>
+  </si>
+  <si>
+    <t>Natazha Cumberbatch</t>
+  </si>
+  <si>
+    <t>kojaniuska@hotmail.com</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>786-683-8709</t>
+  </si>
+  <si>
+    <t>Elian Degen</t>
+  </si>
+  <si>
+    <t>eliandegen@gmail.com</t>
+  </si>
+  <si>
+    <t>786-267-0711</t>
+  </si>
+  <si>
+    <t>Gerald Schwartz</t>
+  </si>
+  <si>
+    <t>786-942-5854</t>
+  </si>
+  <si>
+    <t>Luisasalazar.0914@gmail.com</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>Car 4 Johnny</t>
+  </si>
+  <si>
+    <t>Car 5 Lynette</t>
+  </si>
+  <si>
+    <t>Car 6 Gretchen</t>
+  </si>
+  <si>
+    <t>Car 3 Lisset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiara </t>
+  </si>
+  <si>
+    <t>Chiara+Pilar+Luisa+Monica*+Emily*</t>
+  </si>
+  <si>
+    <t>Shower Tent</t>
+  </si>
+  <si>
+    <t>Lisset</t>
+  </si>
+  <si>
+    <t>Elian</t>
+  </si>
+  <si>
+    <t>Shower RinseKit PRO</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>Pilar+Luisa</t>
+  </si>
+  <si>
+    <t>Diane Gibson</t>
+  </si>
+  <si>
+    <t>dianaalexandragibson@icloud.com</t>
+  </si>
+  <si>
+    <t>303-847-3655</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>Dan+David+Edson+Dulce+Diane</t>
+  </si>
+  <si>
+    <t>Lisset+Elian+Gaby+Natazha+Claudia</t>
+  </si>
+  <si>
+    <t>David+Edson</t>
+  </si>
+  <si>
+    <t>Gretchen+Dulce+Gaby+Natazha+Lisset+Monica+Emily+Diane</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -985,8 +993,12 @@
       <color rgb="FF071444"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1009,6 +1021,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1019,18 +1037,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1044,11 +1060,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1235,461 +1318,466 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="34.33203125" customWidth="1"/>
-    <col min="4" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="1" max="1" width="6" style="12" customWidth="1"/>
+    <col min="2" max="2" width="24" style="12" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="12" customWidth="1"/>
+    <col min="4" max="6" width="10" style="12" customWidth="1"/>
+    <col min="7" max="7" width="30" style="12" customWidth="1"/>
+    <col min="8" max="8" width="16" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="16">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15">
-      <c r="A2" s="2">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="19">
         <v>175.9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15">
-      <c r="A3" s="2">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="19">
         <v>175.9</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15">
-      <c r="A4" s="2">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="19">
         <v>175.9</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="15">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="19">
+        <v>175.9</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D6" s="19">
         <v>175.9</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="G6" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15">
+      <c r="A7" s="10">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D7" s="19">
         <v>175.9</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="G7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15">
+      <c r="A8" s="10">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D8" s="19">
         <v>175.9</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="E8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="19">
+        <v>175.9</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="G9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="D8" s="3">
+      <c r="B10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="19">
         <v>175.9</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="E10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D11" s="19">
         <v>175.9</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="E11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15">
-      <c r="A10" s="2">
+      <c r="G11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15">
+      <c r="A12" s="10">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D12" s="19">
+        <v>175.9</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D13" s="19">
         <v>175.9</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E13" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15">
+      <c r="A14" s="10">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="19">
+        <v>175.9</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="G14" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15">
+      <c r="A15" s="10">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D15" s="19">
         <v>175.9</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="E15" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15">
-      <c r="A12" s="2">
+      <c r="G15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15">
+      <c r="A16" s="10">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="19">
+        <v>175.9</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="G16" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D17" s="19">
         <v>175.9</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="3">
-        <v>175.9</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="E17" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="3">
-        <v>175.9</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="3">
-        <v>175.9</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3">
-        <v>175.9</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="3">
-        <v>175.9</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="2" t="s">
-        <v>73</v>
+      <c r="G17" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C17">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>C2="Paid"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>C2="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>C2="Partial"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1704,40 +1792,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="1" max="1" width="24" style="12" customWidth="1"/>
+    <col min="2" max="2" width="30" style="12" customWidth="1"/>
+    <col min="3" max="4" width="16" style="12" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="16">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>74</v>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15">
-      <c r="A2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>77</v>
+      <c r="A2" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15">
+      <c r="A3" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15">
+      <c r="A4" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1747,262 +1864,546 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="1" max="1" width="24" style="12" customWidth="1"/>
+    <col min="2" max="2" width="8" style="12" customWidth="1"/>
+    <col min="3" max="3" width="24" style="12" customWidth="1"/>
+    <col min="4" max="4" width="10" style="12" customWidth="1"/>
+    <col min="5" max="8" width="8.83203125" style="12"/>
+    <col min="9" max="9" width="13.6640625" style="12" customWidth="1"/>
+    <col min="10" max="10" width="5" style="12" customWidth="1"/>
+    <col min="11" max="11" width="19.6640625" style="12" customWidth="1"/>
+    <col min="12" max="12" width="8.5" style="16" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" style="12" customWidth="1"/>
+    <col min="14" max="14" width="4.83203125" style="12" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" style="12" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" style="16"/>
+    <col min="17" max="16384" width="8.83203125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:16" ht="16">
+      <c r="A1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15">
-      <c r="A2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="D1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="L1" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15">
+      <c r="A2" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="10">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="20" t="str">
+        <f>VLOOKUP(C2,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" s="10">
+        <v>1</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="13">
+        <v>12</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="10">
+        <v>1</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15">
+      <c r="A3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="10">
+        <v>2</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="10" t="str">
+        <f>VLOOKUP(C3,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="10">
+        <v>2</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="13">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15">
-      <c r="A3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="M3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="10">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="O3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="13">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15">
-      <c r="A4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="2">
+    <row r="4" spans="1:16" ht="15">
+      <c r="A4" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="10">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="10" t="str">
+        <f>VLOOKUP(C4,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="10">
+        <v>3</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="13">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="M4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N4" s="10">
+        <v>3</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15">
+      <c r="A5" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="10">
         <v>4</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="C5" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="10" t="str">
+        <f>VLOOKUP(C5,Runners!B:F,5,FALSE)</f>
+        <v>9:00</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="10">
+        <v>4</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="13">
+        <v>11</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N5" s="10">
+        <v>4</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15">
+      <c r="A6" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="10">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="20" t="str">
+        <f>VLOOKUP(C6,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="10">
+        <v>5</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="L6" s="13">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="M6" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N6" s="10">
+        <v>5</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15">
+      <c r="A7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="10">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="C7" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" s="11" t="str">
+        <f>VLOOKUP(C7,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="10">
+        <v>6</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="13">
+        <v>11</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" s="10">
+        <v>6</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="P7" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15">
+      <c r="A8" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="10">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="10" t="str">
+        <f>VLOOKUP(C8,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="10">
+        <v>7</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="13">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="M8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="10">
+        <v>7</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="P8" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15">
+      <c r="A9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="10">
         <v>8</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="D9" s="10" t="str">
+        <f>VLOOKUP(C9,Runners!B:F,5,FALSE)</f>
+        <v>12:00</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="10">
+        <v>8</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="L9" s="14">
+        <v>9</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9" s="10">
+        <v>8</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="P9" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15">
+      <c r="A10" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="10">
         <v>1</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15">
-      <c r="A11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="D10" s="20" t="str">
+        <f>VLOOKUP(C10,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="18">
+        <f>AVERAGE(L2:L9)</f>
+        <v>10.875</v>
+      </c>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="18">
+        <f>AVERAGE(P2:P9)</f>
+        <v>10.875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15">
+      <c r="A11" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="10">
         <v>2</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15">
-      <c r="A12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="C11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="10" t="str">
+        <f>VLOOKUP(C11,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15">
+      <c r="A12" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="10">
         <v>3</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15">
-      <c r="A13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="C12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="10" t="str">
+        <f>VLOOKUP(C12,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15">
+      <c r="A13" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="10">
         <v>4</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15">
-      <c r="A14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="C13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="10" t="str">
+        <f>VLOOKUP(C13,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+      <c r="K13" s="10"/>
+      <c r="L13" s="13"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="13"/>
+    </row>
+    <row r="14" spans="1:16" ht="15">
+      <c r="A14" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="10">
         <v>5</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15">
-      <c r="A15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="C14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="20" t="str">
+        <f>VLOOKUP(C14,Runners!B:F,5,FALSE)</f>
+        <v>13:00</v>
+      </c>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+    </row>
+    <row r="15" spans="1:16" ht="15">
+      <c r="A15" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="10">
         <v>6</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="C15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="10" t="str">
+        <f>VLOOKUP(C15,Runners!B:F,5,FALSE)</f>
+        <v>11:00</v>
+      </c>
+      <c r="K15" s="10"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+    </row>
+    <row r="16" spans="1:16" ht="15">
+      <c r="A16" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="10">
         <v>7</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15">
-      <c r="A17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="C16" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="10" t="str">
+        <f>VLOOKUP(C16,Runners!B:F,5,FALSE)</f>
+        <v>9:00</v>
+      </c>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+    </row>
+    <row r="17" spans="1:16" ht="15">
+      <c r="A17" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="10">
         <v>8</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15">
-      <c r="A18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="2"/>
+      <c r="C17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="10" t="str">
+        <f>VLOOKUP(C17,Runners!B:F,5,FALSE)</f>
+        <v>9:00</v>
+      </c>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="13"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="13"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="K19" s="10"/>
+      <c r="L19" s="13"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="13"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="K20" s="10"/>
+      <c r="L20" s="13"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2026,13 +2427,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
@@ -2045,14 +2446,14 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>89</v>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
@@ -2062,14 +2463,14 @@
       <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>92</v>
+      <c r="C3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15">
@@ -2079,14 +2480,14 @@
       <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>95</v>
+      <c r="C4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15">
@@ -2094,16 +2495,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>97</v>
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15">
@@ -2111,16 +2512,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>97</v>
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15">
@@ -2128,16 +2529,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15">
@@ -2145,16 +2546,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>290</v>
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15">
@@ -2162,16 +2563,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>299</v>
+        <v>39</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15">
@@ -2179,16 +2580,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>103</v>
+        <v>43</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15">
@@ -2196,16 +2597,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>105</v>
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15">
@@ -2213,16 +2614,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>108</v>
+        <v>52</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15">
@@ -2230,16 +2631,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>302</v>
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15">
@@ -2247,16 +2648,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>292</v>
+        <v>275</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15">
@@ -2264,16 +2665,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>288</v>
+        <v>63</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15">
@@ -2281,34 +2682,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>297</v>
+        <v>67</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>294</v>
-      </c>
+      <c r="B17" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="19" spans="1:7">
       <c r="G19" s="2"/>
@@ -2323,212 +2718,348 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="71.6640625" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="1" max="1" width="34" style="12" customWidth="1"/>
+    <col min="2" max="2" width="10" style="12" customWidth="1"/>
+    <col min="3" max="3" width="12" style="12" customWidth="1"/>
+    <col min="4" max="4" width="71.6640625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="8" style="12" customWidth="1"/>
+    <col min="6" max="9" width="8.83203125" style="12"/>
+    <col min="10" max="10" width="27" style="12" customWidth="1"/>
+    <col min="11" max="11" width="7" style="21" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" ht="16">
+      <c r="A1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="10"/>
+      <c r="K1" s="21">
+        <f>SUM(K2:K20)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15">
+      <c r="A2" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D2" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="J2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15">
+      <c r="A3" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E3" s="10">
+        <v>2</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="J3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15">
+      <c r="A4" s="10" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="15">
-      <c r="A2" s="2" t="s">
+      <c r="B4" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E4" s="10">
+        <v>2</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="J4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15">
+      <c r="A5" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B5" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="J5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15">
+      <c r="A6" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E2" s="2">
+      <c r="B6" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="E6" s="10">
+        <v>8</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="J6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15">
+      <c r="A7" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E7" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15">
-      <c r="A3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="G7" s="10"/>
+      <c r="J7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15">
+      <c r="A8" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="2">
+      <c r="B8" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="J8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15">
+      <c r="A9" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="E9" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15">
-      <c r="A4" s="2" t="s">
+      <c r="G9" s="10"/>
+      <c r="J9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15">
+      <c r="A10" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15">
-      <c r="A5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="B10" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="E10" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
-      <c r="A6" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="G10" s="10"/>
+      <c r="J10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15">
-      <c r="A7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15">
-      <c r="A8" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15">
-      <c r="A9" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15">
-      <c r="A10" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" s="2">
+    <row r="11" spans="1:11" ht="15">
+      <c r="E11" s="12">
+        <f>SUM(E2:E10)</f>
+        <v>19</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15">
-      <c r="A11" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" s="2">
+    <row r="12" spans="1:11" ht="15">
+      <c r="D12" s="10"/>
+      <c r="J12" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="E12">
-        <f>SUM(E2:E11)</f>
-        <v>22</v>
-      </c>
+    <row r="13" spans="1:11" ht="15">
+      <c r="J13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15">
+      <c r="J14" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="K14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15">
+      <c r="J15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15">
+      <c r="D16" s="10"/>
+      <c r="J16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="10:11" ht="15">
+      <c r="J17" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="K17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="10:11" ht="15">
+      <c r="J18" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="10:11" ht="15">
+      <c r="J19" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="K19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="10:11" ht="15">
+      <c r="J20" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="K20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="10:11">
+      <c r="K21" s="22"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C2:C11" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" sqref="C2:C10" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"COMPLETE,PENDING,CONFIRM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2538,151 +3069,183 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29.25" customHeight="1">
+    <row r="1" spans="1:9" ht="16">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15">
+        <v>106</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>137</v>
+        <v>291</v>
       </c>
       <c r="D2" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15">
+      <c r="G2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
       <c r="A3" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>139</v>
+        <v>302</v>
       </c>
       <c r="D3" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15">
+      <c r="G3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15">
       <c r="A4" s="2" t="s">
-        <v>140</v>
+        <v>289</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>123</v>
+        <v>303</v>
       </c>
       <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="A5" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="G5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="A6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15">
+    <row r="7" spans="1:9" ht="15">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>288</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>285</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15">
+    <row r="8" spans="1:9" ht="15">
       <c r="A8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B9" s="2" t="s">
+        <f>SUM(D2:D7)</f>
         <v>19</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2">
-        <f>SUM(D2:D9)</f>
-        <v>17</v>
-      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="H15" s="2"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B2:B9" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" sqref="B2:B7" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Pending,Complete,Confirm"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2692,7 +3255,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2705,1790 +3268,1814 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
       <c r="A11" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15">
       <c r="A15" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
       <c r="A16" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15">
       <c r="A17" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15">
       <c r="A18" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
       <c r="A19" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
       <c r="A20" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
       <c r="A21" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
       <c r="A22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15">
       <c r="A23" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15">
       <c r="A24" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="F24" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15">
       <c r="A25" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
       <c r="A26" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
       <c r="A27" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
       <c r="A28" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
       <c r="A29" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15">
       <c r="A32" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15">
       <c r="A33" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15">
       <c r="A34" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15">
       <c r="A35" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15">
       <c r="A36" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
       <c r="A37" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15">
       <c r="A38" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15">
       <c r="A39" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
       <c r="A40" s="2" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15">
       <c r="A41" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15">
       <c r="A42" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15">
       <c r="A43" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15">
       <c r="A44" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15">
       <c r="A45" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15">
       <c r="A46" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15">
       <c r="A47" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15">
       <c r="A48" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15">
       <c r="A49" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15">
       <c r="A50" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15">
       <c r="A51" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15">
       <c r="A52" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15">
       <c r="A53" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15">
       <c r="A54" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15">
       <c r="A55" s="2" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15">
       <c r="A56" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15">
       <c r="A57" s="2" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15">
       <c r="A58" s="2" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15">
       <c r="A59" s="2" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15">
       <c r="A60" s="2" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15">
       <c r="A61" s="2" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15">
       <c r="A62" s="2" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15">
       <c r="A63" s="2" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15">
       <c r="A64" s="2" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15">
       <c r="A65" s="2" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>236</v>
+        <v>292</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>169</v>
+        <v>293</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>189</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15">
       <c r="A66" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>239</v>
+        <v>293</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15">
       <c r="A67" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>241</v>
+        <v>294</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15">
       <c r="A68" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>169</v>
+        <v>216</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15">
       <c r="A69" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15">
       <c r="A70" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15">
       <c r="A71" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15">
       <c r="A72" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15">
       <c r="A73" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15">
       <c r="A74" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15">
       <c r="A75" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15">
       <c r="A76" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15">
       <c r="A77" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15">
       <c r="A78" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15">
       <c r="A79" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15">
       <c r="A80" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15">
       <c r="A81" s="2" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15">
       <c r="A82" s="2" t="s">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15">
       <c r="A83" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15">
       <c r="A84" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="F84" s="2" t="s">
-        <v>189</v>
+        <v>134</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15">
       <c r="A85" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15">
       <c r="A86" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15">
       <c r="A87" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>173</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15">
       <c r="A88" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>263</v>
+        <v>109</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>264</v>
+        <v>150</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15">
       <c r="A89" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E89" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="F89" s="2" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15">
       <c r="A90" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D90" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="E90" s="2"/>
       <c r="F90" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15">
       <c r="A91" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15">
       <c r="A92" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15">
       <c r="A93" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15">
       <c r="A94" s="2" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15">
+      <c r="A95" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4510,23 +5097,23 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15">
       <c r="A2" s="2" t="s">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -4544,62 +5131,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="3" spans="1:5" ht="16">
-      <c r="A3" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B3" s="4"/>
+      <c r="A3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="2" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="2" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="2" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="2" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:5" ht="15">
       <c r="A8" s="2" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:5" ht="15">
       <c r="A9" s="2" t="s">
-        <v>284</v>
+        <v>259</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>286</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C00FBA-8A26-0046-AD07-431DEDBA2790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBA3C21-6C48-364C-8DAF-1293A02EC5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="660" windowWidth="33620" windowHeight="17440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="306">
   <si>
     <t>#</t>
   </si>
@@ -691,12 +691,6 @@
     <t>Toilet Bags</t>
   </si>
   <si>
-    <t>I think we have lifetime supply</t>
-  </si>
-  <si>
-    <t>Toilet Paper</t>
-  </si>
-  <si>
     <t>Deodorant</t>
   </si>
   <si>
@@ -959,6 +953,12 @@
   </si>
   <si>
     <t>Gretchen+Dulce+Gaby+Natazha+Lisset+Monica+Emily+Diane</t>
+  </si>
+  <si>
+    <t>We might need to order another box</t>
+  </si>
+  <si>
+    <t>Toilet Paper Roll</t>
   </si>
 </sst>
 </file>
@@ -968,7 +968,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -1041,7 +1041,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1055,11 +1055,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1067,9 +1062,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1099,39 +1091,20 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1318,466 +1291,466 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="6" style="12" customWidth="1"/>
-    <col min="2" max="2" width="24" style="12" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="12" customWidth="1"/>
-    <col min="4" max="6" width="10" style="12" customWidth="1"/>
-    <col min="7" max="7" width="30" style="12" customWidth="1"/>
-    <col min="8" max="8" width="16" style="12" customWidth="1"/>
-    <col min="9" max="16384" width="8.83203125" style="12"/>
+    <col min="1" max="1" width="6" style="8" customWidth="1"/>
+    <col min="2" max="2" width="24" style="8" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="8" customWidth="1"/>
+    <col min="4" max="6" width="10" style="8" customWidth="1"/>
+    <col min="7" max="7" width="30" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16" style="8" customWidth="1"/>
+    <col min="9" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15">
-      <c r="A2" s="10">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="15">
         <v>175.9</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15">
-      <c r="A3" s="10">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="15">
         <v>175.9</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15">
-      <c r="A4" s="10">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="15">
         <v>175.9</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15">
-      <c r="A5" s="10">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="15">
         <v>175.9</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15">
-      <c r="A6" s="10">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="15">
         <v>175.9</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="G6" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15">
-      <c r="A7" s="10">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="15">
         <v>175.9</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15">
-      <c r="A8" s="10">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="15">
         <v>175.9</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15">
-      <c r="A9" s="10">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="15">
         <v>175.9</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15">
-      <c r="A10" s="10">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="15">
         <v>175.9</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15">
-      <c r="A11" s="10">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="15">
         <v>175.9</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="7" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15">
-      <c r="A12" s="10">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="15">
         <v>175.9</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15">
-      <c r="A13" s="10">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="15">
         <v>175.9</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15">
-      <c r="A14" s="10">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="15">
+        <v>175.9</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="F14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D15" s="15">
         <v>175.9</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15">
-      <c r="A15" s="10">
-        <v>14</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="E15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D16" s="15">
         <v>175.9</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="10" t="s">
+      <c r="E16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15">
-      <c r="A16" s="10">
-        <v>15</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="G16" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15">
+      <c r="A17" s="7">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D17" s="15">
         <v>175.9</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="10" t="s">
+      <c r="E17" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15">
-      <c r="A17" s="10">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="s">
+      <c r="G17" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="H17" s="7" t="s">
         <v>298</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="19">
-        <v>175.9</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>300</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C17">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>C2="Paid"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>C2="Pending"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>C2="Partial"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1795,65 +1768,65 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24" style="12" customWidth="1"/>
-    <col min="2" max="2" width="30" style="12" customWidth="1"/>
-    <col min="3" max="4" width="16" style="12" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="12"/>
+    <col min="1" max="1" width="24" style="8" customWidth="1"/>
+    <col min="2" max="2" width="30" style="8" customWidth="1"/>
+    <col min="3" max="4" width="16" style="8" customWidth="1"/>
+    <col min="5" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1867,543 +1840,543 @@
   <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24" style="12" customWidth="1"/>
-    <col min="2" max="2" width="8" style="12" customWidth="1"/>
-    <col min="3" max="3" width="24" style="12" customWidth="1"/>
-    <col min="4" max="4" width="10" style="12" customWidth="1"/>
-    <col min="5" max="8" width="8.83203125" style="12"/>
-    <col min="9" max="9" width="13.6640625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="5" style="12" customWidth="1"/>
-    <col min="11" max="11" width="19.6640625" style="12" customWidth="1"/>
-    <col min="12" max="12" width="8.5" style="16" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" style="12" customWidth="1"/>
-    <col min="14" max="14" width="4.83203125" style="12" customWidth="1"/>
-    <col min="15" max="15" width="27.6640625" style="12" customWidth="1"/>
-    <col min="16" max="16" width="8.83203125" style="16"/>
-    <col min="17" max="16384" width="8.83203125" style="12"/>
+    <col min="1" max="1" width="24" style="8" customWidth="1"/>
+    <col min="2" max="2" width="8" style="8" customWidth="1"/>
+    <col min="3" max="3" width="24" style="8" customWidth="1"/>
+    <col min="4" max="4" width="10" style="8" customWidth="1"/>
+    <col min="5" max="8" width="8.83203125" style="8"/>
+    <col min="9" max="9" width="13.6640625" style="8" customWidth="1"/>
+    <col min="10" max="10" width="5" style="8" customWidth="1"/>
+    <col min="11" max="11" width="19.6640625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="8.5" style="12" customWidth="1"/>
+    <col min="13" max="13" width="16.83203125" style="8" customWidth="1"/>
+    <col min="14" max="14" width="4.83203125" style="8" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" style="8" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" style="12"/>
+    <col min="17" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="16">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="11" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="20" t="str">
+      <c r="D2" s="16" t="str">
         <f>VLOOKUP(C2,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="7">
         <v>1</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="9">
         <v>12</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="7">
         <v>1</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="9">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="15">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="10" t="str">
+      <c r="D3" s="7" t="str">
         <f>VLOOKUP(C3,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="7">
         <v>2</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="9">
         <v>11</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="7">
         <v>2</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="13">
+      <c r="P3" s="9">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>3</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="10" t="str">
+      <c r="D4" s="7" t="str">
         <f>VLOOKUP(C4,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="7">
         <v>3</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="9">
         <v>11</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="7">
         <v>3</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="9">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>4</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5" s="10" t="str">
+      <c r="C5" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D5" s="7" t="str">
         <f>VLOOKUP(C5,Runners!B:F,5,FALSE)</f>
         <v>9:00</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="7">
         <v>4</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="9">
         <v>11</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="7">
         <v>4</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="9">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>5</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="20" t="str">
+      <c r="D6" s="16" t="str">
         <f>VLOOKUP(C6,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="7">
         <v>5</v>
       </c>
-      <c r="K6" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="L6" s="13">
+      <c r="K6" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="L6" s="9">
         <v>11</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="7">
         <v>5</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="P6" s="13">
+      <c r="P6" s="9">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>6</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="11" t="str">
+      <c r="C7" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" s="7" t="str">
         <f>VLOOKUP(C7,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="7">
         <v>6</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="9">
         <v>11</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="7">
         <v>6</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="P7" s="13">
+      <c r="P7" s="9">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>7</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="10" t="str">
+      <c r="D8" s="7" t="str">
         <f>VLOOKUP(C8,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="7">
         <v>7</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="9">
         <v>11</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="7">
         <v>7</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="9">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="7">
         <v>8</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="10" t="str">
+      <c r="D9" s="7" t="str">
         <f>VLOOKUP(C9,Runners!B:F,5,FALSE)</f>
         <v>12:00</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="7">
         <v>8</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="L9" s="14">
+      <c r="K9" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="L9" s="10">
         <v>9</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9" s="7">
         <v>8</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="9">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="15">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="7">
         <v>1</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="20" t="str">
+      <c r="D10" s="16" t="str">
         <f>VLOOKUP(C10,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="18">
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="14">
         <f>AVERAGE(L2:L9)</f>
         <v>10.875</v>
       </c>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="18">
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="14">
         <f>AVERAGE(P2:P9)</f>
         <v>10.875</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="15">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="7">
         <v>2</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="10" t="str">
+      <c r="D11" s="7" t="str">
         <f>VLOOKUP(C11,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="7">
         <v>3</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="10" t="str">
+      <c r="D12" s="7" t="str">
         <f>VLOOKUP(C12,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="7">
         <v>4</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="10" t="str">
+      <c r="D13" s="7" t="str">
         <f>VLOOKUP(C13,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="13"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="13"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="9"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="9"/>
     </row>
     <row r="14" spans="1:16" ht="15">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="7">
         <v>5</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="20" t="str">
+      <c r="D14" s="16" t="str">
         <f>VLOOKUP(C14,Runners!B:F,5,FALSE)</f>
         <v>13:00</v>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" spans="1:16" ht="15">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="7">
         <v>6</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="10" t="str">
+      <c r="D15" s="7" t="str">
         <f>VLOOKUP(C15,Runners!B:F,5,FALSE)</f>
         <v>11:00</v>
       </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
     </row>
     <row r="16" spans="1:16" ht="15">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="7">
         <v>7</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="10" t="str">
+      <c r="D16" s="7" t="str">
         <f>VLOOKUP(C16,Runners!B:F,5,FALSE)</f>
         <v>9:00</v>
       </c>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
     </row>
     <row r="17" spans="1:16" ht="15">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="7">
         <v>8</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="10" t="str">
+      <c r="D17" s="7" t="str">
         <f>VLOOKUP(C17,Runners!B:F,5,FALSE)</f>
         <v>9:00</v>
       </c>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="13"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="9"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="13"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="9"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="K19" s="10"/>
-      <c r="L19" s="13"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="13"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="9"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="9"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="K20" s="10"/>
-      <c r="L20" s="13"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="13"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="9"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2501,7 +2474,7 @@
         <v>89</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>90</v>
@@ -2518,7 +2491,7 @@
         <v>89</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>90</v>
@@ -2549,13 +2522,13 @@
         <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15">
@@ -2566,13 +2539,13 @@
         <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15">
@@ -2634,13 +2607,13 @@
         <v>56</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15">
@@ -2648,16 +2621,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15">
@@ -2668,13 +2641,13 @@
         <v>63</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15">
@@ -2685,21 +2658,21 @@
         <v>67</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>298</v>
+      <c r="B17" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -2718,344 +2691,223 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="34" style="12" customWidth="1"/>
-    <col min="2" max="2" width="10" style="12" customWidth="1"/>
-    <col min="3" max="3" width="12" style="12" customWidth="1"/>
-    <col min="4" max="4" width="71.6640625" style="12" customWidth="1"/>
-    <col min="5" max="5" width="8" style="12" customWidth="1"/>
-    <col min="6" max="9" width="8.83203125" style="12"/>
-    <col min="10" max="10" width="27" style="12" customWidth="1"/>
-    <col min="11" max="11" width="7" style="21" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="12"/>
+    <col min="1" max="1" width="34" style="8" customWidth="1"/>
+    <col min="2" max="2" width="10" style="8" customWidth="1"/>
+    <col min="3" max="3" width="12" style="8" customWidth="1"/>
+    <col min="4" max="4" width="71.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="8" style="8" customWidth="1"/>
+    <col min="6" max="9" width="8.83203125" style="8"/>
+    <col min="10" max="10" width="27" style="8" customWidth="1"/>
+    <col min="11" max="11" width="7" style="17" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="21">
-        <f>SUM(K2:K20)</f>
-        <v>19</v>
-      </c>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:11" ht="15">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="J2" s="10" t="s">
+      <c r="E2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="18"/>
+    </row>
+    <row r="3" spans="1:11" ht="15">
+      <c r="A3" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="7">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="18"/>
+    </row>
+    <row r="4" spans="1:11" ht="15">
+      <c r="A4" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="7">
+        <v>2</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="18"/>
+    </row>
+    <row r="5" spans="1:11" ht="15">
+      <c r="A5" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="18"/>
+    </row>
+    <row r="6" spans="1:11" ht="15">
+      <c r="A6" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E6" s="7">
         <v>8</v>
       </c>
-      <c r="K2" s="22">
+      <c r="G6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="18"/>
+    </row>
+    <row r="7" spans="1:11" ht="15">
+      <c r="A7" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="18"/>
+    </row>
+    <row r="8" spans="1:11" ht="15">
+      <c r="A8" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E8" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="15">
-      <c r="A3" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="G8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="18"/>
+    </row>
+    <row r="9" spans="1:11" ht="15">
+      <c r="A9" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C9" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="D9" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="E9" s="7">
         <v>2</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="J3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="22">
+      <c r="G9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="1:11" ht="15">
+      <c r="A10" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="15">
-      <c r="A4" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="10">
-        <v>2</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="J4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15">
-      <c r="A5" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="10">
-        <v>1</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="J5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15">
-      <c r="A6" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="E6" s="10">
-        <v>8</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="J6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15">
-      <c r="A7" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="E7" s="10">
-        <v>2</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="J7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15">
-      <c r="A8" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="E8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="J8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15">
-      <c r="A9" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="E9" s="10">
-        <v>2</v>
-      </c>
-      <c r="G9" s="10"/>
-      <c r="J9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15">
-      <c r="A10" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="E10" s="10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="J10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15">
-      <c r="E11" s="12">
+      <c r="G10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="18"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="E11" s="8">
         <f>SUM(E2:E10)</f>
         <v>19</v>
       </c>
-      <c r="J11" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15">
-      <c r="D12" s="10"/>
-      <c r="J12" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15">
-      <c r="J13" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K13" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15">
-      <c r="J14" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="K14" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15">
-      <c r="J15" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K15" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15">
-      <c r="D16" s="10"/>
-      <c r="J16" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="K16" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="10:11" ht="15">
-      <c r="J17" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="K17" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="10:11" ht="15">
-      <c r="J18" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="10:11" ht="15">
-      <c r="J19" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K19" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="10:11" ht="15">
-      <c r="J20" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="K20" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="10:11">
-      <c r="K21" s="22"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="18"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3095,13 +2947,13 @@
       <c r="D1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3110,10 +2962,10 @@
         <v>122</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D2" s="2">
         <v>5</v>
@@ -3133,10 +2985,10 @@
         <v>123</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D3" s="2">
         <v>5</v>
@@ -3148,18 +3000,18 @@
         <v>63</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15">
       <c r="A4" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D4" s="2">
         <v>5</v>
@@ -3171,15 +3023,15 @@
         <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15">
       <c r="A5" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>116</v>
@@ -3190,8 +3042,8 @@
       <c r="G5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>298</v>
+      <c r="H5" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
@@ -3199,10 +3051,10 @@
     </row>
     <row r="6" spans="1:9" ht="15">
       <c r="A6" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>114</v>
@@ -3213,10 +3065,10 @@
     </row>
     <row r="7" spans="1:9" ht="15">
       <c r="A7" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>124</v>
@@ -3258,1823 +3110,1818 @@
   <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="43.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.1640625" customWidth="1"/>
-    <col min="4" max="4" width="27.83203125" customWidth="1"/>
-    <col min="5" max="5" width="32.83203125" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16" style="8" customWidth="1"/>
+    <col min="2" max="2" width="43.6640625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="27.83203125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="32.83203125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="7" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C11" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="E13" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="E15" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="C19" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
+      <c r="C20" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2" t="s">
+      <c r="C21" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="C22" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="E22" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="C23" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="E23" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="C24" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="E25" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="E26" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="E27" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="E29" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="C30" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2" t="s">
+      <c r="C31" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15">
+      <c r="A33" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15">
+      <c r="A34" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15">
+      <c r="A35" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15">
+      <c r="A36" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15">
+      <c r="A37" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15">
+      <c r="A38" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15">
+      <c r="A39" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15">
+      <c r="A40" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15">
+      <c r="A41" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15">
+      <c r="A42" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15">
+      <c r="A43" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15">
+      <c r="A44" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15">
+      <c r="A45" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15">
+      <c r="A46" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15">
+      <c r="A47" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15">
+      <c r="A48" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15">
+      <c r="A49" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15">
+      <c r="A50" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15">
+      <c r="A51" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15">
+      <c r="A52" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15">
+      <c r="A53" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15">
+      <c r="A54" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15">
+      <c r="A55" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15">
+      <c r="A56" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15">
+      <c r="A57" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15">
+      <c r="A58" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15">
+      <c r="A59" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15">
+      <c r="A60" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15">
+      <c r="A61" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15">
+      <c r="A62" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15">
+      <c r="A63" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15">
+      <c r="A64" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15">
+      <c r="A65" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="F65" s="7" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15">
-      <c r="A32" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2" t="s">
+    <row r="66" spans="1:6" ht="15">
+      <c r="A66" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="F66" s="7" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15">
-      <c r="A33" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2" t="s">
+    <row r="67" spans="1:6" ht="15">
+      <c r="A67" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15">
+      <c r="A68" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F68" s="7"/>
+    </row>
+    <row r="69" spans="1:6" ht="15">
+      <c r="A69" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15">
+      <c r="A70" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15">
+      <c r="A71" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15">
+      <c r="A72" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15">
+      <c r="A73" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F73" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15">
-      <c r="A34" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
+    <row r="74" spans="1:6" ht="15">
+      <c r="A74" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F74" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15">
-      <c r="A35" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2" t="s">
+    <row r="75" spans="1:6" ht="15">
+      <c r="A75" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F75" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15">
-      <c r="A36" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2" t="s">
+    <row r="76" spans="1:6" ht="15">
+      <c r="A76" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F76" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15">
-      <c r="A37" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2" t="s">
+    <row r="77" spans="1:6" ht="15">
+      <c r="A77" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F77" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15">
-      <c r="A38" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2" t="s">
+    <row r="78" spans="1:6" ht="15">
+      <c r="A78" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F78" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15">
-      <c r="A39" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2" t="s">
+    <row r="79" spans="1:6" ht="15">
+      <c r="A79" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F79" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15">
-      <c r="A40" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
+    <row r="80" spans="1:6" ht="15">
+      <c r="A80" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F80" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15">
-      <c r="A41" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C41" s="2" t="s">
+    <row r="81" spans="1:6" ht="15">
+      <c r="A81" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15">
+      <c r="A82" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15">
+      <c r="A83" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="D83" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15">
+      <c r="A84" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15">
+      <c r="A85" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15">
+      <c r="A86" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15">
+      <c r="A87" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15">
+      <c r="A88" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F88" s="7"/>
+    </row>
+    <row r="89" spans="1:6" ht="15">
+      <c r="A89" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F89" s="7" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15">
-      <c r="A42" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F42" s="2" t="s">
+    <row r="90" spans="1:6" ht="15">
+      <c r="A90" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15">
-      <c r="A43" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="15">
-      <c r="A44" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C44" s="2" t="s">
+    <row r="91" spans="1:6" ht="15">
+      <c r="A91" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="15">
+      <c r="A92" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C92" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15">
-      <c r="A45" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15">
-      <c r="A46" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="15">
+      <c r="A93" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C93" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15">
-      <c r="A47" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C47" s="2" t="s">
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15">
+      <c r="A94" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C94" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="15">
-      <c r="A48" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15">
+      <c r="A95" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C95" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15">
-      <c r="A49" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15">
-      <c r="A50" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15">
-      <c r="A51" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15">
-      <c r="A52" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15">
-      <c r="A53" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15">
-      <c r="A54" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15">
-      <c r="A55" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15">
-      <c r="A56" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15">
-      <c r="A57" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="15">
-      <c r="A58" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="15">
-      <c r="A59" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15">
-      <c r="A60" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15">
-      <c r="A61" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15">
-      <c r="A62" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="15">
-      <c r="A63" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="15">
-      <c r="A64" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="15">
-      <c r="A65" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15">
-      <c r="A66" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="15">
-      <c r="A67" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="15">
-      <c r="A68" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15">
-      <c r="A69" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15">
-      <c r="A70" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15">
-      <c r="A71" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15">
-      <c r="A72" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="15">
-      <c r="A73" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15">
-      <c r="A74" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15">
-      <c r="A75" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15">
-      <c r="A76" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15">
-      <c r="A77" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="15">
-      <c r="A78" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="15">
-      <c r="A79" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="15">
-      <c r="A80" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="15">
-      <c r="A81" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="15">
-      <c r="A82" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="15">
-      <c r="A83" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="15">
-      <c r="A84" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15">
-      <c r="A85" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="15">
-      <c r="A86" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="15">
-      <c r="A87" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15">
-      <c r="A88" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15">
-      <c r="A89" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15">
-      <c r="A90" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="15">
-      <c r="A91" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="15">
-      <c r="A92" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="15">
-      <c r="A93" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="15">
-      <c r="A94" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="15">
-      <c r="A95" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2" t="s">
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7" t="s">
         <v>134</v>
       </c>
     </row>
@@ -5097,23 +4944,23 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15">
       <c r="A2" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -5131,62 +4978,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="A1" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="15">
       <c r="A4" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:5" ht="15">
       <c r="A8" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:5" ht="15">
       <c r="A9" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/Relay2026_Data.xlsx
+++ b/Relay2026_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBA3C21-6C48-364C-8DAF-1293A02EC5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17C0E738-1FD2-7A4F-B751-E3241A878DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="660" windowWidth="33620" windowHeight="17440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="940" yWindow="660" windowWidth="33620" windowHeight="17440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runners" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="306">
   <si>
     <t>#</t>
   </si>
@@ -1288,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" style="8" customWidth="1"/>
@@ -1297,10 +1297,12 @@
     <col min="4" max="6" width="10" style="8" customWidth="1"/>
     <col min="7" max="7" width="30" style="8" customWidth="1"/>
     <col min="8" max="8" width="16" style="8" customWidth="1"/>
-    <col min="9" max="16384" width="8.83203125" style="8"/>
+    <col min="9" max="10" width="8.83203125" style="8"/>
+    <col min="11" max="11" width="28" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16">
+    <row r="1" spans="1:11" ht="16">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1326,7 +1328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15">
+    <row r="2" spans="1:11" ht="15">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1351,8 +1353,11 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15">
+      <c r="K2" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1377,8 +1382,11 @@
       <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15">
+      <c r="K3" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1403,8 +1411,11 @@
       <c r="H4" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="15">
+      <c r="K4" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1429,8 +1440,11 @@
       <c r="H5" s="7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15">
+      <c r="K5" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -1455,8 +1469,11 @@
       <c r="H6" s="7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="15">
+      <c r="K6" s="7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -1481,8 +1498,11 @@
       <c r="H7" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="15">
+      <c r="K7" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -1507,8 +1527,11 @@
       <c r="H8" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="15">
+      <c r="K8" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -1533,8 +1556,11 @@
       <c r="H9" s="7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="15">
+      <c r="K9" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -1560,7 +1586,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15">
+    <row r="11" spans="1:11" ht="15">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -1586,7 +1612,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15">
+    <row r="12" spans="1:11" ht="15">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -1612,7 +1638,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15">
+    <row r="13" spans="1:11" ht="15">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -1638,7 +1664,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15">
+    <row r="14" spans="1:11" ht="15">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -1664,7 +1690,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15">
+    <row r="15" spans="1:11" ht="15">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -1690,7 +1716,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15">
+    <row r="16" spans="1:11" ht="15">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -1837,7 +1863,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="24" style="8" customWidth="1"/>
@@ -1849,14 +1875,16 @@
     <col min="10" max="10" width="5" style="8" customWidth="1"/>
     <col min="11" max="11" width="19.6640625" style="8" customWidth="1"/>
     <col min="12" max="12" width="8.5" style="12" customWidth="1"/>
-    <col min="13" max="13" width="16.83203125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="4.83203125" style="8" customWidth="1"/>
-    <col min="15" max="15" width="27.6640625" style="8" customWidth="1"/>
-    <col min="16" max="16" width="8.83203125" style="12"/>
-    <col min="17" max="16384" width="8.83203125" style="8"/>
+    <col min="13" max="13" width="20.5" style="12" customWidth="1"/>
+    <col min="14" max="14" width="8.5" style="12" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" style="8" customWidth="1"/>
+    <col min="16" max="16" width="4.83203125" style="8" customWidth="1"/>
+    <col min="17" max="17" width="27.6640625" style="8" customWidth="1"/>
+    <col min="18" max="18" width="8.83203125" style="12"/>
+    <col min="19" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16">
+    <row r="1" spans="1:18" ht="16">
       <c r="A1" s="6" t="s">
         <v>73</v>
       </c>
@@ -1881,20 +1909,22 @@
       <c r="L1" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="R1" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15">
+    <row r="2" spans="1:18" ht="15">
       <c r="A2" s="7" t="s">
         <v>75</v>
       </c>
@@ -1920,20 +1950,22 @@
       <c r="L2" s="9">
         <v>12</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N2" s="7">
+      <c r="P2" s="7">
         <v>1</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="Q2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="9">
+      <c r="R2" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15">
+    <row r="3" spans="1:18" ht="15">
       <c r="A3" s="7" t="s">
         <v>75</v>
       </c>
@@ -1959,20 +1991,22 @@
       <c r="L3" s="9">
         <v>11</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="7">
+      <c r="P3" s="7">
         <v>2</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="9">
+      <c r="R3" s="9">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15">
+    <row r="4" spans="1:18" ht="15">
       <c r="A4" s="7" t="s">
         <v>75</v>
       </c>
@@ -1998,20 +2032,22 @@
       <c r="L4" s="9">
         <v>11</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="7">
+      <c r="P4" s="7">
         <v>3</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="9">
+      <c r="R4" s="9">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15">
+    <row r="5" spans="1:18" ht="15">
       <c r="A5" s="7" t="s">
         <v>75</v>
       </c>
@@ -2019,11 +2055,11 @@
         <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>273</v>
+        <v>56</v>
       </c>
       <c r="D5" s="7" t="str">
         <f>VLOOKUP(C5,Runners!B:F,5,FALSE)</f>
-        <v>9:00</v>
+        <v>11:00</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>75</v>
@@ -2037,20 +2073,22 @@
       <c r="L5" s="9">
         <v>11</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N5" s="7">
+      <c r="P5" s="7">
         <v>4</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="Q5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="9">
+      <c r="R5" s="9">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15">
+    <row r="6" spans="1:18" ht="15">
       <c r="A6" s="7" t="s">
         <v>75</v>
       </c>
@@ -2058,7 +2096,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>56</v>
+        <v>296</v>
       </c>
       <c r="D6" s="16" t="str">
         <f>VLOOKUP(C6,Runners!B:F,5,FALSE)</f>
@@ -2076,20 +2114,22 @@
       <c r="L6" s="9">
         <v>11</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N6" s="7">
+      <c r="P6" s="7">
         <v>5</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="Q6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="P6" s="9">
+      <c r="R6" s="9">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15">
+    <row r="7" spans="1:18" ht="15">
       <c r="A7" s="7" t="s">
         <v>75</v>
       </c>
@@ -2097,11 +2137,11 @@
         <v>6</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>296</v>
+        <v>18</v>
       </c>
       <c r="D7" s="7" t="str">
         <f>VLOOKUP(C7,Runners!B:F,5,FALSE)</f>
-        <v>11:00</v>
+        <v>12:00</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>75</v>
@@ -2115,20 +2155,22 @@
       <c r="L7" s="9">
         <v>11</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N7" s="7">
+      <c r="P7" s="7">
         <v>6</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="Q7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="P7" s="9">
+      <c r="R7" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15">
+    <row r="8" spans="1:18" ht="15">
       <c r="A8" s="7" t="s">
         <v>75</v>
       </c>
@@ -2154,20 +2196,22 @@
       <c r="L8" s="9">
         <v>11</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N8" s="7">
+      <c r="P8" s="7">
         <v>7</v>
       </c>
-      <c r="O8" s="7" t="s">
+      <c r="Q8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="P8" s="9">
+      <c r="R8" s="9">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15">
+    <row r="9" spans="1:18" ht="15">
       <c r="A9" s="7" t="s">
         <v>75</v>
       </c>
@@ -2175,11 +2219,11 @@
         <v>8</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>18</v>
+        <v>273</v>
       </c>
       <c r="D9" s="7" t="str">
         <f>VLOOKUP(C9,Runners!B:F,5,FALSE)</f>
-        <v>12:00</v>
+        <v>9:00</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>75</v>
@@ -2193,20 +2237,22 @@
       <c r="L9" s="10">
         <v>9</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="N9" s="7">
+      <c r="P9" s="7">
         <v>8</v>
       </c>
-      <c r="O9" s="7" t="s">
+      <c r="Q9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="P9" s="9">
+      <c r="R9" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15">
+    <row r="10" spans="1:18" ht="15">
       <c r="A10" s="7" t="s">
         <v>76</v>
       </c>
@@ -2227,15 +2273,17 @@
         <f>AVERAGE(L2:L9)</f>
         <v>10.875</v>
       </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
       <c r="O10" s="13"/>
-      <c r="P10" s="14">
-        <f>AVERAGE(P2:P9)</f>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="14">
+        <f>AVERAGE(R2:R9)</f>
         <v>10.875</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15">
+    <row r="11" spans="1:18" ht="15">
       <c r="A11" s="7" t="s">
         <v>76</v>
       </c>
@@ -2250,7 +2298,7 @@
         <v>11:00</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15">
+    <row r="12" spans="1:18" ht="15">
       <c r="A12" s="7" t="s">
         <v>76</v>
       </c>
@@ -2265,7 +2313,7 @@
         <v>11:00</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15">
+    <row r="13" spans="1:18" ht="15">
       <c r="A13" s="7" t="s">
         <v>76</v>
       </c>
@@ -2273,7 +2321,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D13" s="7" t="str">
         <f>VLOOKUP(C13,Runners!B:F,5,FALSE)</f>
@@ -2281,10 +2329,12 @@
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="9"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="9"/>
-    </row>
-    <row r="14" spans="1:16" ht="15">
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="9"/>
+    </row>
+    <row r="14" spans="1:18" ht="15">
       <c r="A14" s="7" t="s">
         <v>76</v>
       </c>
@@ -2292,16 +2342,16 @@
         <v>5</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D14" s="16" t="str">
         <f>VLOOKUP(C14,Runners!B:F,5,FALSE)</f>
-        <v>13:00</v>
-      </c>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-    </row>
-    <row r="15" spans="1:16" ht="15">
+        <v>11:00</v>
+      </c>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+    </row>
+    <row r="15" spans="1:18" ht="15">
       <c r="A15" s="7" t="s">
         <v>76</v>
       </c>
@@ -2309,18 +2359,20 @@
         <v>6</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D15" s="7" t="str">
         <f>VLOOKUP(C15,Runners!B:F,5,FALSE)</f>
-        <v>11:00</v>
+        <v>9:00</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="9"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-    </row>
-    <row r="16" spans="1:16" ht="15">
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+    </row>
+    <row r="16" spans="1:18" ht="15">
       <c r="A16" s="7" t="s">
         <v>76</v>
       </c>
@@ -2328,16 +2380,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D16" s="7" t="str">
         <f>VLOOKUP(C16,Runners!B:F,5,FALSE)</f>
-        <v>9:00</v>
-      </c>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-    </row>
-    <row r="17" spans="1:16" ht="15">
+        <v>13:00</v>
+      </c>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+    </row>
+    <row r="17" spans="1:18" ht="15">
       <c r="A17" s="7" t="s">
         <v>76</v>
       </c>
@@ -2351,32 +2403,36 @@
         <f>VLOOKUP(C17,Runners!B:F,5,FALSE)</f>
         <v>9:00</v>
       </c>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="9"/>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="9"/>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
       <c r="O18" s="7"/>
-      <c r="P18" s="9"/>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="9"/>
+    </row>
+    <row r="19" spans="1:18">
       <c r="K19" s="7"/>
       <c r="L19" s="9"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="9"/>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="9"/>
+    </row>
+    <row r="20" spans="1:18">
       <c r="K20" s="7"/>
       <c r="L20" s="9"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
